--- a/artfynd/A 13548-2024 artfynd.xlsx
+++ b/artfynd/A 13548-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112550260</v>
+        <v>112550258</v>
       </c>
       <c r="B2" t="n">
-        <v>89625</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527986</v>
+        <v>527934</v>
       </c>
       <c r="R2" t="n">
-        <v>6986868</v>
+        <v>6986891</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -793,37 +788,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112550259</v>
+        <v>112550251</v>
       </c>
       <c r="B3" t="n">
-        <v>78743</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93196</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>1435</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -837,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527967</v>
+        <v>528068</v>
       </c>
       <c r="R3" t="n">
-        <v>6986873</v>
+        <v>6986906</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -911,15 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112550258</v>
+        <v>112550256</v>
       </c>
       <c r="B4" t="n">
-        <v>77417</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,21 +912,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -955,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527934</v>
+        <v>527911</v>
       </c>
       <c r="R4" t="n">
-        <v>6986891</v>
+        <v>6986876</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1029,15 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112550263</v>
+        <v>112550261</v>
       </c>
       <c r="B5" t="n">
-        <v>77498</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1045,21 +1025,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1073,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528021</v>
+        <v>527987</v>
       </c>
       <c r="R5" t="n">
-        <v>6986909</v>
+        <v>6986905</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1147,37 +1127,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112550256</v>
+        <v>112550260</v>
       </c>
       <c r="B6" t="n">
-        <v>90916</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1191,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527911</v>
+        <v>527986</v>
       </c>
       <c r="R6" t="n">
-        <v>6986876</v>
+        <v>6986868</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1268,12 +1243,7 @@
         <v>112550257</v>
       </c>
       <c r="B7" t="n">
-        <v>90945</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1383,15 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112550261</v>
+        <v>112550263</v>
       </c>
       <c r="B8" t="n">
-        <v>90916</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1399,21 +1364,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1427,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527987</v>
+        <v>528021</v>
       </c>
       <c r="R8" t="n">
-        <v>6986905</v>
+        <v>6986909</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1494,6 +1459,119 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>112550259</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sönner knackåstjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>527967</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6986873</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 13548-2024 artfynd.xlsx
+++ b/artfynd/A 13548-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550258</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550251</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550256</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550261</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1262,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550260</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1350,6 +1380,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550257</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1463,6 +1498,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550263</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1576,8 +1616,23 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550259</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>